--- a/InputData/indst/_cement/BFoCDMbNI/BAU Fraction of Clinker Demand Met by Net Imports.xlsx
+++ b/InputData/indst/_cement/BFoCDMbNI/BAU Fraction of Clinker Demand Met by Net Imports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\BFoCDMbNI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E877699-16AF-4E3B-8388-74A51DDF0BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6E8272-B97C-46F5-9DD5-5EE6FA5F7942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="162">
   <si>
     <t>BFoCDMbNI BAU Fraction of Clinker Demand Met by Net Imports</t>
   </si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>Domestic clinker production (kt)</t>
-  </si>
-  <si>
-    <t>Net import share (rounded to 4 decimals)</t>
   </si>
   <si>
     <t>&lt;- 2025 anchor, used by the Regions US row</t>
@@ -473,9 +470,6 @@
     <t>U.S. values</t>
   </si>
   <si>
-    <t>For the U.S. national file version, the share for 2021-2025 is one minus domestic clinker production divided by apparent consumption times the blend ratio, all from USGS. It rises from 0.196 in 2021 to 0.244 in 2025, in line with USGS's rising net import reliance, and this closes the start-year balance so the model's 2025 domestic clinker equals USGS's 69.0 million tons. From 2026 the share is held flat at the 2025 value, which is our judgment; no import response to prices or policy is modeled. As a cross-check, building the share up from reported imports and exports gives 0.207 for 2025. The gap comes from USGS rounding apparent consumption to two significant figures and from the 2025 drawdown in cement stocks (9.7 to 8.2 million tons).</t>
-  </si>
-  <si>
     <t>Other regions' values</t>
   </si>
   <si>
@@ -498,6 +492,40 @@
   </si>
   <si>
     <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>Net import share</t>
+  </si>
+  <si>
+    <t>Longer import history and the outlook</t>
+  </si>
+  <si>
+    <t>Argus Media</t>
+  </si>
+  <si>
+    <t>US cement market 2026 outlook shaky (Intercem Americas)</t>
+  </si>
+  <si>
+    <t>https://www.argusmedia.com/news-and-insights/latest-market-news/2758546-us-cement-market-2026-outlook-shaky</t>
+  </si>
+  <si>
+    <t>Industry forecasters expected consumption to bottom near 100 million tons in 2026 with plants running at about 76% and import terminal additions continuing. Combined with USGS data for 2001-2025, the share on this file's basis was 0.26 at the 2006 peak, 0.06-0.08 in 2009-2014, and back to 0.20-0.24 in 2021-2025.</t>
+  </si>
+  <si>
+    <t>Recent import trends and trade policy</t>
+  </si>
+  <si>
+    <t>Tariffs in July 2026</t>
+  </si>
+  <si>
+    <t>https://www.globalcement.com/news/analysis/21057-tariffs-in-july-2026</t>
+  </si>
+  <si>
+    <t>Imports grew from 13.5 million tons (2017) to 25.4 million tons (2025). Emergency tariffs were struck down in February 2026; first-half 2026 imports were 11.9 million tons, about flat on 2025 (Argus, August 2026).</t>
+  </si>
+  <si>
+    <t>For 2021-2025 the share is one minus domestic clinker production divided by apparent consumption times the blend ratio, all from USGS. It rises from 0.196 in 2021 to 0.244 in 2025, in line with USGS's rising net import reliance, and this closes the start-year balance so the model's 2025 domestic clinker equals USGS's 69.0 million tons.
+From 2026 the share is held at the 2025 value. Nothing points clearly up or down: announced U.S. kiln additions through 2027 are roughly offset by closures, domestic plants would run at about 66% in 2029 and 78% by 2050 at a flat share (near past peaks of about 80%), and tariffs and new import terminals push in opposite directions. No source publishes a forward projection, so a reasonable range is 0.18-0.30 by 2050, which moves 2050 domestic clinker by about +/-8%. No import response to prices or policy is modeled. As a cross-check, building the 2025 share up from reported imports and exports gives 0.207; the gap comes from USGS rounding apparent consumption to two significant figures and from the 2025 drawdown in cement stocks (9.7 to 8.2 million tons).</t>
   </si>
 </sst>
 </file>
@@ -577,7 +605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -598,6 +626,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -903,408 +934,458 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D64"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="110.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="110.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="D5" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="10">
         <v>2026</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="10">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B14" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="10">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+      <c r="D24" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="D25" s="10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="D26" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
+      <c r="D28" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="B29" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B35" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="10">
         <v>2026</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D41" s="10">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B43" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="10">
         <v>2025</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
+      <c r="D48" s="10">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B49" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B50" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B52" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B53" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="10">
         <v>2025</v>
       </c>
-      <c r="D20" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
-        <v>2026</v>
-      </c>
-      <c r="D27" s="2">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="2">
-        <v>2025</v>
-      </c>
-      <c r="D34" s="2">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+      <c r="D55" s="10"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B56" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="2">
-        <v>2025</v>
-      </c>
-      <c r="D41" s="2">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B42" s="9" t="s">
+      <c r="D56" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B57" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="2">
-        <v>2026</v>
-      </c>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B49" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="9" t="s">
+      <c r="D57" s="10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="2" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="B61" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B54" s="2" t="s">
+    </row>
+    <row r="62" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="B62" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="2" t="s">
+    </row>
+    <row r="63" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="B63" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B64" s="10" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="150" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{96658F58-EC84-4EF8-9C38-BBAB7DC90B3D}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{B36E3D72-BBC6-4B05-A53D-723291F15569}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{76A54CF6-94C8-452C-B71A-C54F9D1DD4E1}"/>
-    <hyperlink ref="B28" r:id="rId4" xr:uid="{D73B310C-98A6-4A38-841D-7F38FF92F882}"/>
-    <hyperlink ref="B35" r:id="rId5" xr:uid="{3E2D453F-C8FD-4651-8583-A4CE68D5FF34}"/>
-    <hyperlink ref="B42" r:id="rId6" xr:uid="{C3262373-8CC5-42E8-817B-88C69B975279}"/>
-    <hyperlink ref="B49" r:id="rId7" xr:uid="{7CD7B2E5-BA98-49A4-BE56-ECA6C1E7B747}"/>
-    <hyperlink ref="D7" r:id="rId8" xr:uid="{69C75C50-086C-400B-BAAB-E641742552DA}"/>
-    <hyperlink ref="D14" r:id="rId9" xr:uid="{16731DE3-0B6A-4975-A0B9-4EA201791C8B}"/>
-    <hyperlink ref="D21" r:id="rId10" xr:uid="{765C360C-4318-4816-A05D-D1F97A965931}"/>
-    <hyperlink ref="D28" r:id="rId11" xr:uid="{E171D064-FE0D-43F2-8F3C-D7BEB345CBE5}"/>
-    <hyperlink ref="D35" r:id="rId12" xr:uid="{BEE0F5D2-0A21-4D55-BCA2-8E8B04DFB678}"/>
-    <hyperlink ref="D42" r:id="rId13" xr:uid="{5CCA4BFD-DEBF-4754-A41F-67139CB5FC18}"/>
-    <hyperlink ref="D49" r:id="rId14" xr:uid="{3A7EB453-036F-447C-BF97-70C557CB1D15}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{09D04C90-C30D-4F68-9107-281CC66D53FF}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{E04CDC8D-FE42-41CE-8965-FB94886F80BA}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{0D16EFB0-BDBD-42B5-90C8-8D618F9A43AC}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{AE52B43A-379C-43B7-B2BD-36118D5EF70A}"/>
+    <hyperlink ref="B35" r:id="rId5" xr:uid="{DD266204-B249-4430-82AA-AAAFCDB12B8D}"/>
+    <hyperlink ref="B42" r:id="rId6" xr:uid="{E1DA003A-6578-4F3B-AE62-0E50E47EE57E}"/>
+    <hyperlink ref="B49" r:id="rId7" xr:uid="{E49CFE4B-1F40-4783-BC0A-989EEBBC3450}"/>
+    <hyperlink ref="B56" r:id="rId8" xr:uid="{2E15D8B5-9021-4A25-AD32-6D4E39B3E55B}"/>
+    <hyperlink ref="D7" r:id="rId9" xr:uid="{1800B7C6-448B-4A4D-A2C5-BFF3354F871E}"/>
+    <hyperlink ref="D14" r:id="rId10" xr:uid="{0B416381-BD8C-4E6D-AB5E-7BF79C105E4E}"/>
+    <hyperlink ref="D21" r:id="rId11" xr:uid="{890FADC6-6F2B-4F48-B983-80BEC7CB4E2F}"/>
+    <hyperlink ref="D28" r:id="rId12" xr:uid="{A68171BC-DB91-48B3-A4AB-DF5B4D1453CD}"/>
+    <hyperlink ref="D35" r:id="rId13" xr:uid="{87D23A45-14AD-4936-B2DA-36AC43228921}"/>
+    <hyperlink ref="D42" r:id="rId14" xr:uid="{C626E993-7AED-4FD5-8282-9DD1CBB086B6}"/>
+    <hyperlink ref="D49" r:id="rId15" xr:uid="{70E4295D-7D54-4482-AE1F-E5B6C363FD1D}"/>
+    <hyperlink ref="D56" r:id="rId16" xr:uid="{65723EBE-84DF-48DF-8574-F044EB66DEA1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1313,7 +1394,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1322,7 +1403,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1330,12 +1411,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1352,7 +1433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1361,7 +1442,7 @@
       </c>
       <c r="C5">
         <f>Derivation!G10</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1370,7 +1451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1378,8 +1459,8 @@
         <v>2024</v>
       </c>
       <c r="C6">
-        <f>ROUND(((0.06-5.02)+(0.28-0.34))/1858.9,3)</f>
-        <v>-3.0000000000000001E-3</v>
+        <f>(((0.06-5.02)+(0.28-0.34))/1858.9)</f>
+        <v>-2.7005218139760068E-3</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
@@ -1388,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1396,17 +1477,17 @@
         <v>2024</v>
       </c>
       <c r="C7">
-        <f>ROUND(((0.74-0.98)*0.73+(1.55-0.02))/(435*0.73),3)</f>
-        <v>4.0000000000000001E-3</v>
+        <f>(((0.74-0.98)*0.73+(1.55-0.02))/(435*0.73))</f>
+        <v>4.2664147378365614E-3</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1414,8 +1495,8 @@
         <v>2024</v>
       </c>
       <c r="C8">
-        <f>ROUND((11.3-11.2)/148.1,3)</f>
-        <v>1E-3</v>
+        <f>((11.3-11.2)/148.1)</f>
+        <v>6.752194463200636E-4</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1424,7 +1505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1435,7 +1516,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1443,8 +1524,8 @@
         <v>2024</v>
       </c>
       <c r="C10">
-        <f>ROUND(((0.14-0.07)*0.71+0.92)/(64.8*0.71),3)</f>
-        <v>2.1000000000000001E-2</v>
+        <f>(((0.14-0.07)*0.71+0.92)/(64.8*0.71))</f>
+        <v>2.1076769257520434E-2</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -1453,7 +1534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1461,17 +1542,17 @@
         <v>2024</v>
       </c>
       <c r="C11">
-        <f>ROUND(((0.1-1.38)*0.75+0)/(42*0.75),3)</f>
-        <v>-0.03</v>
+        <f>(((0.1-1.38)*0.75+0)/(42*0.75))</f>
+        <v>-3.0476190476190473E-2</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1479,17 +1560,17 @@
         <v>2024</v>
       </c>
       <c r="C12">
-        <f>ROUND(((1.2-4.39)*0.89-0.47)/((12.7+1.2-(4.39+0.47))*0.89),3)</f>
-        <v>-0.41099999999999998</v>
+        <f>(((1.2-4.39)*0.89-0.47)/((12.7+1.2-(4.39+0.47))*0.89))</f>
+        <v>-0.41129312916376659</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1497,17 +1578,17 @@
         <v>2025</v>
       </c>
       <c r="C13">
-        <f>ROUND(-(12.34+1.32*0.68)/(57.301-12.34),3)</f>
-        <v>-0.29399999999999998</v>
+        <f>(-(12.34+1.32*0.68)/(57.301-12.34))</f>
+        <v>-0.29442405640443942</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1528,17 +1609,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1558,7 +1639,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1578,7 +1659,7 @@
         <v>84000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1598,7 +1679,7 @@
         <v>69000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1618,7 +1699,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1638,7 +1719,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -1658,7 +1739,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1678,7 +1759,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1698,7 +1779,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1718,7 +1799,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1738,7 +1819,7 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1758,7 +1839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1775,7 +1856,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1792,7 +1873,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1809,7 +1890,7 @@
         <v>61000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1826,7 +1907,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1843,7 +1924,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1860,7 +1941,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1877,7 +1958,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -1894,7 +1975,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1911,7 +1992,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1928,7 +2009,7 @@
         <v>62000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1945,7 +2026,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1962,7 +2043,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1979,7 +2060,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1996,7 +2077,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>53</v>
       </c>
@@ -2013,7 +2094,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -2030,7 +2111,7 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>55</v>
       </c>
@@ -2055,12 +2136,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AE14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -2069,16 +2150,16 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
       <c r="B2">
         <f>IF(ISNUMBER(INDEX(Regions!$C$5:$C$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0))),INDEX(Regions!$C$5:$C$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0)),0)</f>
-        <v>0.24360000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.24359877848249933</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2087,12 +2168,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -2112,57 +2193,57 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>61</v>
       </c>
       <c r="B7">
-        <f>ROUND(('USGS MCS 2026 Cement'!B5+'USGS MCS 2026 Cement'!B8)/'USGS MCS 2026 Cement'!B4,4)</f>
-        <v>0.8921</v>
+        <f>(('USGS MCS 2026 Cement'!B5+'USGS MCS 2026 Cement'!B8)/'USGS MCS 2026 Cement'!B4)</f>
+        <v>0.8920769230769231</v>
       </c>
       <c r="C7">
-        <f>ROUND(('USGS MCS 2026 Cement'!C5+'USGS MCS 2026 Cement'!C8)/'USGS MCS 2026 Cement'!C4,4)</f>
-        <v>0.88280000000000003</v>
+        <f>(('USGS MCS 2026 Cement'!C5+'USGS MCS 2026 Cement'!C8)/'USGS MCS 2026 Cement'!C4)</f>
+        <v>0.8827850877192982</v>
       </c>
       <c r="D7">
-        <f>ROUND(('USGS MCS 2026 Cement'!D5+'USGS MCS 2026 Cement'!D8)/'USGS MCS 2026 Cement'!D4,4)</f>
-        <v>0.86629999999999996</v>
+        <f>(('USGS MCS 2026 Cement'!D5+'USGS MCS 2026 Cement'!D8)/'USGS MCS 2026 Cement'!D4)</f>
+        <v>0.86633221850613151</v>
       </c>
       <c r="E7">
-        <f>ROUND(('USGS MCS 2026 Cement'!E5+'USGS MCS 2026 Cement'!E8)/'USGS MCS 2026 Cement'!E4,4)</f>
-        <v>0.85509999999999997</v>
+        <f>(('USGS MCS 2026 Cement'!E5+'USGS MCS 2026 Cement'!E8)/'USGS MCS 2026 Cement'!E4)</f>
+        <v>0.85511764705882354</v>
       </c>
       <c r="F7">
-        <f>ROUND(('USGS MCS 2026 Cement'!F5+'USGS MCS 2026 Cement'!F8)/'USGS MCS 2026 Cement'!F4,4)</f>
-        <v>0.82930000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+        <f>(('USGS MCS 2026 Cement'!F5+'USGS MCS 2026 Cement'!F8)/'USGS MCS 2026 Cement'!F4)</f>
+        <v>0.82928571428571429</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>62</v>
       </c>
       <c r="B8">
         <f>'USGS MCS 2026 Cement'!B10*B7</f>
-        <v>99023.1</v>
+        <v>99020.538461538468</v>
       </c>
       <c r="C8">
         <f>'USGS MCS 2026 Cement'!C10*C7</f>
-        <v>100639.2</v>
+        <v>100637.5</v>
       </c>
       <c r="D8">
         <f>'USGS MCS 2026 Cement'!D10*D7</f>
-        <v>97891.9</v>
+        <v>97895.540691192859</v>
       </c>
       <c r="E8">
         <f>'USGS MCS 2026 Cement'!E10*E7</f>
-        <v>94061</v>
+        <v>94062.941176470587</v>
       </c>
       <c r="F8">
         <f>'USGS MCS 2026 Cement'!F10*F7</f>
-        <v>91223</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+        <v>91221.428571428565</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -2187,64 +2268,64 @@
         <v>69000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="B10">
-        <f>ROUND(1-B9/B8,4)</f>
-        <v>0.19600000000000001</v>
+        <f>(1-B9/B8)</f>
+        <v>0.19596478430659692</v>
       </c>
       <c r="C10">
-        <f>ROUND(1-C9/C8,4)</f>
-        <v>0.2102</v>
+        <f>(1-C9/C8)</f>
+        <v>0.21014532356229043</v>
       </c>
       <c r="D10">
-        <f>ROUND(1-D9/D8,4)</f>
-        <v>0.21560000000000001</v>
+        <f>(1-D9/D8)</f>
+        <v>0.2156026775292299</v>
       </c>
       <c r="E10">
-        <f>ROUND(1-E9/E8,4)</f>
-        <v>0.23449999999999999</v>
+        <f>(1-E9/E8)</f>
+        <v>0.23455508514323953</v>
       </c>
       <c r="F10">
-        <f>ROUND(1-F9/F8,4)</f>
-        <v>0.24360000000000001</v>
+        <f>(1-F9/F8)</f>
+        <v>0.24359877848249933</v>
       </c>
       <c r="G10">
         <f>F10</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="H10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>66</v>
       </c>
       <c r="B11">
         <f>('USGS MCS 2026 Cement'!B7*B7+'USGS MCS 2026 Cement'!B8-'USGS MCS 2026 Cement'!B9*B7)/B8</f>
-        <v>0.18693734896200986</v>
+        <v>0.18693775727956979</v>
       </c>
       <c r="C11">
         <f>('USGS MCS 2026 Cement'!C7*C7+'USGS MCS 2026 Cement'!C8-'USGS MCS 2026 Cement'!C9*C7)/C8</f>
-        <v>0.22138199429248245</v>
+        <v>0.22138216566755353</v>
       </c>
       <c r="D11">
         <f>('USGS MCS 2026 Cement'!D7*D7+'USGS MCS 2026 Cement'!D8-'USGS MCS 2026 Cement'!D9*D7)/D8</f>
-        <v>0.22265612476619617</v>
+        <v>0.22265577487436275</v>
       </c>
       <c r="E11">
         <f>('USGS MCS 2026 Cement'!E7*E7+'USGS MCS 2026 Cement'!E8-'USGS MCS 2026 Cement'!E9*E7)/E8</f>
-        <v>0.21403705361414402</v>
+        <v>0.21403690332505768</v>
       </c>
       <c r="F11">
         <f>('USGS MCS 2026 Cement'!F7*F7+'USGS MCS 2026 Cement'!F8-'USGS MCS 2026 Cement'!F9*F7)/F8</f>
-        <v>0.20723501748462561</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.20723514211886307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -2339,129 +2420,129 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14">
         <f>IF($B$3=1,B10,$B$2)</f>
-        <v>0.19600000000000001</v>
+        <v>0.19596478430659692</v>
       </c>
       <c r="C14">
         <f>IF($B$3=1,C10,$B$2)</f>
-        <v>0.2102</v>
+        <v>0.21014532356229043</v>
       </c>
       <c r="D14">
         <f>IF($B$3=1,D10,$B$2)</f>
-        <v>0.21560000000000001</v>
+        <v>0.2156026775292299</v>
       </c>
       <c r="E14">
         <f>IF($B$3=1,E10,$B$2)</f>
-        <v>0.23449999999999999</v>
+        <v>0.23455508514323953</v>
       </c>
       <c r="F14">
         <f>IF($B$3=1,F10,$B$2)</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="G14">
         <f t="shared" ref="G14:AE14" si="0">$B$2</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="K14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="L14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="M14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="N14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="P14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="Q14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="R14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="T14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="U14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="V14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="W14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="X14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="Y14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AA14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AB14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AC14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AD14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AE14">
         <f t="shared" si="0"/>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
     </row>
   </sheetData>
@@ -2472,29 +2553,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="70.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <f>'USGS MCS 2026 Cement'!F10*Derivation!F7*(1-Derivation!F10)</f>
-        <v>69001.0772</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>69000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" t="str">
         <f>IF(ISNUMBER(INDEX(Regions!$C$5:$C$14,MATCH(Regions!$B$1,Regions!$A$5:$A$14,0))),"PASS","WARN - blank row treated as 0 (self-sufficient)")</f>
@@ -2512,11 +2593,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -2609,129 +2690,129 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <f>Derivation!B14</f>
-        <v>0.19600000000000001</v>
+        <v>0.19596478430659692</v>
       </c>
       <c r="C2">
         <f>Derivation!C14</f>
-        <v>0.2102</v>
+        <v>0.21014532356229043</v>
       </c>
       <c r="D2">
         <f>Derivation!D14</f>
-        <v>0.21560000000000001</v>
+        <v>0.2156026775292299</v>
       </c>
       <c r="E2">
         <f>Derivation!E14</f>
-        <v>0.23449999999999999</v>
+        <v>0.23455508514323953</v>
       </c>
       <c r="F2">
         <f>Derivation!F14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="G2">
         <f>Derivation!G14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="H2">
         <f>Derivation!H14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="I2">
         <f>Derivation!I14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="J2">
         <f>Derivation!J14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="K2">
         <f>Derivation!K14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="L2">
         <f>Derivation!L14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="M2">
         <f>Derivation!M14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="N2">
         <f>Derivation!N14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="O2">
         <f>Derivation!O14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="P2">
         <f>Derivation!P14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="Q2">
         <f>Derivation!Q14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="R2">
         <f>Derivation!R14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="S2">
         <f>Derivation!S14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="T2">
         <f>Derivation!T14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="U2">
         <f>Derivation!U14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="V2">
         <f>Derivation!V14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="W2">
         <f>Derivation!W14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="X2">
         <f>Derivation!X14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="Y2">
         <f>Derivation!Y14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="Z2">
         <f>Derivation!Z14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AA2">
         <f>Derivation!AA14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AB2">
         <f>Derivation!AB14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AC2">
         <f>Derivation!AC14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AD2">
         <f>Derivation!AD14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
       <c r="AE2">
         <f>Derivation!AE14</f>
-        <v>0.24360000000000001</v>
+        <v>0.24359877848249933</v>
       </c>
     </row>
   </sheetData>
